--- a/Available Data from Temghar Unit.xlsx
+++ b/Available Data from Temghar Unit.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Encure IT System\AMS AI System\asset-management\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="M:\Encure IT System Project\AMS AI System\asset-management\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A2C3AD7-D80C-4180-A6EE-9A10A647AA2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53E73F55-62BB-4EBF-8D26-338D090DBD19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="3" r:id="rId3"/>
+    <pivotCache cacheId="7" r:id="rId3"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="277">
   <si>
     <t>Supplier Name</t>
   </si>
@@ -49,9 +49,6 @@
     <t>Location</t>
   </si>
   <si>
-    <t>Asset Group</t>
-  </si>
-  <si>
     <t>Rate</t>
   </si>
   <si>
@@ -136,9 +133,6 @@
     <t>(S.E Elec) Office</t>
   </si>
   <si>
-    <t>Dinesh Laskhare</t>
-  </si>
-  <si>
     <t>Furniture and Fixture</t>
   </si>
   <si>
@@ -448,9 +442,6 @@
     <t>HP Printer</t>
   </si>
   <si>
-    <t>Arpit Santosh Agarwal</t>
-  </si>
-  <si>
     <t xml:space="preserve">Air conditioner </t>
   </si>
   <si>
@@ -814,9 +805,6 @@
     <t>Asset Name</t>
   </si>
   <si>
-    <t>Exact Location</t>
-  </si>
-  <si>
     <t>Asset Availability status</t>
   </si>
   <si>
@@ -878,6 +866,12 @@
   </si>
   <si>
     <t>Warranty Date</t>
+  </si>
+  <si>
+    <t>Admin User</t>
+  </si>
+  <si>
+    <t>Asset Type</t>
   </si>
 </sst>
 </file>
@@ -6691,7 +6685,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{410D7024-0B92-42B4-8D07-B2A4C0B8D941}" name="PivotTable9" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{410D7024-0B92-42B4-8D07-B2A4C0B8D941}" name="PivotTable9" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A3:E189" firstHeaderRow="1" firstDataRow="1" firstDataCol="4"/>
   <pivotFields count="22">
     <pivotField name="Assets Name]" axis="axisRow" compact="0" outline="0" showAll="0">
@@ -15759,22 +15753,22 @@
   <sheetData>
     <row r="1" spans="1:31" ht="40.799999999999997" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>257</v>
+        <v>1</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>0</v>
@@ -15783,111 +15777,111 @@
         <v>1</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>2</v>
+        <v>276</v>
       </c>
       <c r="J1" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>259</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="U1" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="V1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>270</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>267</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>271</v>
+      </c>
+      <c r="AB1" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="AC1" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="L1" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="N1" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="O1" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="P1" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="Q1" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="R1" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="T1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="U1" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="V1" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>274</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="Z1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>95</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="AB1" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="AC1" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:31" ht="33" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B2" s="3">
         <v>12345</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F2" s="3">
         <v>83</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>100</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>277</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>102</v>
       </c>
       <c r="M2" s="12">
         <v>41781</v>
@@ -15907,13 +15901,13 @@
         <v>10</v>
       </c>
       <c r="R2" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S2" s="14">
         <v>46049</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="U2" s="20">
         <v>27441</v>
@@ -15922,68 +15916,68 @@
         <v>2277603</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X2" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y2" s="2" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="Z2" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AA2" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB2" s="15" t="str">
         <f>RIGHT(Z2,7)</f>
         <v xml:space="preserve"> 421101</v>
       </c>
       <c r="AC2" s="15" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="AD2" s="16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="AE2" s="3"/>
     </row>
     <row r="3" spans="1:31" ht="54" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3">
         <v>12346</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F3" s="3">
         <v>1</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M3" s="17">
         <v>42017</v>
@@ -16003,13 +15997,13 @@
         <v>15</v>
       </c>
       <c r="R3" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S3" s="14">
         <v>46041</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="U3" s="13">
         <v>425465</v>
@@ -16018,69 +16012,69 @@
         <v>425465</v>
       </c>
       <c r="W3" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X3" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y3" s="2">
         <v>9867772203</v>
       </c>
       <c r="Z3" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AA3" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB3" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC3" s="15" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:31" ht="54" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3">
         <v>12347</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F4" s="3">
         <v>1</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M4" s="17">
         <v>43549</v>
@@ -16100,13 +16094,13 @@
         <v>15</v>
       </c>
       <c r="R4" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S4" s="14">
         <v>46041</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="U4" s="13">
         <v>650472</v>
@@ -16115,69 +16109,69 @@
         <v>650472</v>
       </c>
       <c r="W4" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4" s="2">
         <v>9867772203</v>
       </c>
       <c r="Z4" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AA4" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB4" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC4" s="15" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="AD4" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="AE4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3">
         <v>12348</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F5" s="3">
         <v>1</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M5" s="17">
         <v>43544</v>
@@ -16197,13 +16191,13 @@
         <v>10</v>
       </c>
       <c r="R5" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S5" s="14">
         <v>46045</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U5" s="13">
         <v>31426</v>
@@ -16212,70 +16206,70 @@
         <v>31426</v>
       </c>
       <c r="W5" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X5" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y5" s="1">
         <v>9930806006</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA5" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB5" s="15" t="str">
         <f t="shared" ref="AB5:AB28" si="2">RIGHT(Z5,7)</f>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC5" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD5" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE5" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3">
         <v>12349</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M6" s="17">
         <v>43544</v>
@@ -16295,13 +16289,13 @@
         <v>10</v>
       </c>
       <c r="R6" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S6" s="14">
         <v>46045</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U6" s="13">
         <v>31426</v>
@@ -16310,70 +16304,70 @@
         <v>31426</v>
       </c>
       <c r="W6" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X6" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y6" s="1">
         <v>9930806006</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA6" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB6" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC6" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD6" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE6" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3">
         <v>12350</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F7" s="3">
         <v>1</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M7" s="17">
         <v>43544</v>
@@ -16393,13 +16387,13 @@
         <v>10</v>
       </c>
       <c r="R7" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S7" s="14">
         <v>46045</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U7" s="13">
         <v>31426</v>
@@ -16408,70 +16402,70 @@
         <v>31426</v>
       </c>
       <c r="W7" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X7" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y7" s="1">
         <v>9930806006</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB7" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC7" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD7" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE7" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B8" s="3">
         <v>12351</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F8" s="3">
         <v>1</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M8" s="17">
         <v>43544</v>
@@ -16491,13 +16485,13 @@
         <v>10</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S8" s="14">
         <v>46045</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U8" s="13">
         <v>53908</v>
@@ -16506,70 +16500,70 @@
         <v>53908</v>
       </c>
       <c r="W8" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X8" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y8" s="1">
         <v>9930806006</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA8" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB8" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC8" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD8" s="3" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AE8" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="9" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B9" s="3">
         <v>12352</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F9" s="3">
         <v>8</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M9" s="17">
         <v>43544</v>
@@ -16589,13 +16583,13 @@
         <v>10</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S9" s="14">
         <v>46045</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U9" s="13">
         <v>8931</v>
@@ -16604,70 +16598,70 @@
         <v>71448</v>
       </c>
       <c r="W9" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X9" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y9" s="1">
         <v>9930806006</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA9" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB9" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC9" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD9" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE9" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B10" s="3">
         <v>12353</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F10" s="3">
         <v>1</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M10" s="12">
         <v>45194</v>
@@ -16687,13 +16681,13 @@
         <v>3</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S10" s="14">
         <v>46032</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="U10" s="20">
         <v>55440</v>
@@ -16702,70 +16696,70 @@
         <v>55440</v>
       </c>
       <c r="W10" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X10" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y10" s="1" t="s">
+      <c r="Z10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Z10" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="AA10" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB10" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400601</v>
       </c>
       <c r="AC10" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE10" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B11" s="3">
         <v>12354</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F11" s="3">
         <v>1</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M11" s="17">
         <v>43614</v>
@@ -16785,13 +16779,13 @@
         <v>10</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S11" s="14">
         <v>46042</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="U11" s="13">
         <v>34568.231428571402</v>
@@ -16800,69 +16794,69 @@
         <v>34568.231428571402</v>
       </c>
       <c r="W11" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X11" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y11" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z11" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA11" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB11" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC11" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD11" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B12" s="3">
         <v>12355</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F12" s="3">
         <v>1</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M12" s="17">
         <v>43614</v>
@@ -16882,13 +16876,13 @@
         <v>10</v>
       </c>
       <c r="R12" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S12" s="14">
         <v>46042</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="U12" s="13">
         <v>34568.231428571402</v>
@@ -16897,69 +16891,69 @@
         <v>34568.231428571402</v>
       </c>
       <c r="W12" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X12" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z12" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA12" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC12" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD12" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B13" s="3">
         <v>12356</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F13" s="3">
         <v>1</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M13" s="17">
         <v>43614</v>
@@ -16979,13 +16973,13 @@
         <v>10</v>
       </c>
       <c r="R13" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S13" s="14">
         <v>46042</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="U13" s="13">
         <v>34567.231428571431</v>
@@ -16994,69 +16988,69 @@
         <v>34567.231428571431</v>
       </c>
       <c r="W13" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X13" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z13" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA13" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB13" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC13" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD13" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:31" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="3">
         <v>12357</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F14" s="3">
         <v>1</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M14" s="12">
         <v>45280</v>
@@ -17076,13 +17070,13 @@
         <v>3</v>
       </c>
       <c r="R14" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S14" s="14">
         <v>46032</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="U14" s="13">
         <v>19305</v>
@@ -17091,70 +17085,70 @@
         <v>19305</v>
       </c>
       <c r="W14" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X14" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y14" s="1" t="s">
+      <c r="Z14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Z14" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="AA14" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB14" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400601</v>
       </c>
       <c r="AC14" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B15" s="3">
         <v>12358</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F15" s="3">
         <v>1</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M15" s="17">
         <v>43614</v>
@@ -17174,13 +17168,13 @@
         <v>10</v>
       </c>
       <c r="R15" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S15" s="14">
         <v>46045</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="U15" s="13">
         <v>34568.231428571402</v>
@@ -17189,65 +17183,65 @@
         <v>34568.231428571402</v>
       </c>
       <c r="W15" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X15" s="3"/>
       <c r="Y15" s="3"/>
       <c r="Z15" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA15" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB15" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC15" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD15" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE15" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B16" s="3">
         <v>12359</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F16" s="3">
         <v>1</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M16" s="18">
         <v>43544</v>
@@ -17267,13 +17261,13 @@
         <v>10</v>
       </c>
       <c r="R16" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S16" s="14">
         <v>46045</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U16" s="13">
         <v>62722</v>
@@ -17282,70 +17276,70 @@
         <v>62722</v>
       </c>
       <c r="W16" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X16" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y16" s="1">
         <v>9930806006</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA16" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB16" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC16" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD16" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE16" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B17" s="3">
         <v>12360</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F17" s="3">
         <v>1</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M17" s="17">
         <v>43544</v>
@@ -17365,13 +17359,13 @@
         <v>5</v>
       </c>
       <c r="R17" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S17" s="14">
         <v>46042</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U17" s="20">
         <v>31426</v>
@@ -17380,70 +17374,70 @@
         <v>31426</v>
       </c>
       <c r="W17" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X17" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y17" s="1">
         <v>9930806006</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA17" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB17" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC17" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD17" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE17" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B18" s="3">
         <v>12361</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F18" s="3">
         <v>1</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M18" s="18">
         <v>43544</v>
@@ -17463,13 +17457,13 @@
         <v>10</v>
       </c>
       <c r="R18" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S18" s="14">
         <v>46045</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U18" s="13">
         <v>62722</v>
@@ -17478,70 +17472,70 @@
         <v>62722</v>
       </c>
       <c r="W18" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X18" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y18" s="1">
         <v>9930806006</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA18" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB18" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC18" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD18" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE18" s="6" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="19" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B19" s="3">
         <v>12362</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F19" s="3">
         <v>1</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M19" s="18">
         <v>43544</v>
@@ -17561,13 +17555,13 @@
         <v>10</v>
       </c>
       <c r="R19" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S19" s="14">
         <v>46045</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U19" s="13">
         <v>62722</v>
@@ -17576,70 +17570,70 @@
         <v>62722</v>
       </c>
       <c r="W19" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X19" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y19" s="1">
         <v>9930806006</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA19" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB19" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC19" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD19" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE19" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="20" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B20" s="3">
         <v>12363</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F20" s="3">
         <v>1</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M20" s="17">
         <v>43544</v>
@@ -17659,13 +17653,13 @@
         <v>10</v>
       </c>
       <c r="R20" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S20" s="14">
         <v>46042</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="U20" s="20">
         <v>31426</v>
@@ -17674,70 +17668,70 @@
         <v>31426</v>
       </c>
       <c r="W20" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X20" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y20" s="1">
         <v>9930806006</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA20" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB20" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC20" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD20" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AE20" s="3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:31" ht="21.6" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B21" s="3">
         <v>12364</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="E21" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="F21" s="3">
         <v>2</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M21" s="17">
         <v>43033</v>
@@ -17757,13 +17751,13 @@
         <v>5</v>
       </c>
       <c r="R21" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S21" s="14">
         <v>46045</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="U21" s="13">
         <v>135535.88888888888</v>
@@ -17772,69 +17766,69 @@
         <v>271071.77777777775</v>
       </c>
       <c r="W21" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X21" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y21" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Z21" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AA21" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB21" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AC21" s="15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AD21" s="3" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="AE21" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:31" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B22" s="3">
         <v>12365</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F22" s="3">
         <v>1</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M22" s="12">
         <v>45495</v>
@@ -17854,13 +17848,13 @@
         <v>3</v>
       </c>
       <c r="R22" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S22" s="14">
         <v>46041</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="U22" s="20">
         <v>52100</v>
@@ -17869,70 +17863,70 @@
         <v>52100</v>
       </c>
       <c r="W22" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X22" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y22" s="1" t="s">
+      <c r="Z22" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Z22" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="AA22" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB22" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400601</v>
       </c>
       <c r="AC22" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AE22" s="6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:31" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B23" s="3">
         <v>12366</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F23" s="3">
         <v>1</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M23" s="12">
         <v>45191</v>
@@ -17952,13 +17946,13 @@
         <v>3</v>
       </c>
       <c r="R23" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S23" s="14">
         <v>46032</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="U23" s="20">
         <v>13516</v>
@@ -17967,70 +17961,70 @@
         <v>13516</v>
       </c>
       <c r="W23" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X23" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Y23" s="1" t="s">
+      <c r="Z23" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="Z23" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="AA23" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB23" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400601</v>
       </c>
       <c r="AC23" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD23" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE23" s="6" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" ht="32.4" x14ac:dyDescent="0.3">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" ht="22.2" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B24" s="3">
         <v>12367</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F24" s="3">
         <v>1</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M24" s="19">
         <v>44968</v>
@@ -18050,13 +18044,13 @@
         <v>10</v>
       </c>
       <c r="R24" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S24" s="19">
         <v>46032</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="U24" s="20">
         <v>8201</v>
@@ -18065,70 +18059,70 @@
         <v>8201</v>
       </c>
       <c r="W24" s="3" t="s">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="X24" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y24" s="1">
         <v>9930806009</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA24" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB24" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC24" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE24" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" ht="32.4" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" ht="22.2" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B25" s="3">
         <v>12368</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F25" s="3">
         <v>3</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M25" s="19">
         <v>44968</v>
@@ -18148,13 +18142,13 @@
         <v>10</v>
       </c>
       <c r="R25" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S25" s="19">
         <v>46032</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="U25" s="20">
         <v>7611</v>
@@ -18163,70 +18157,70 @@
         <v>22833</v>
       </c>
       <c r="W25" s="3" t="s">
-        <v>135</v>
+        <v>275</v>
       </c>
       <c r="X25" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y25" s="1">
         <v>9930806009</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA25" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB25" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC25" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE25" s="7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:31" ht="32.4" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" s="3">
         <v>12369</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="F26" s="3">
         <v>1</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M26" s="19">
         <v>45151</v>
@@ -18246,7 +18240,7 @@
         <v>3</v>
       </c>
       <c r="R26" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S26" s="14">
         <v>46032</v>
@@ -18260,71 +18254,71 @@
       <c r="V26" s="20">
         <v>50000</v>
       </c>
-      <c r="W26" s="1" t="s">
-        <v>31</v>
+      <c r="W26" s="3" t="s">
+        <v>275</v>
       </c>
       <c r="X26" s="7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y26" s="1">
         <v>9324349923</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AA26" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB26" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400601</v>
       </c>
       <c r="AC26" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE26" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:31" ht="22.2" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3">
         <v>12370</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F27" s="3">
         <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M27" s="19">
         <v>44968</v>
@@ -18344,13 +18338,13 @@
         <v>10</v>
       </c>
       <c r="R27" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S27" s="19">
         <v>46032</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="U27" s="20">
         <v>8201</v>
@@ -18359,70 +18353,70 @@
         <v>8201</v>
       </c>
       <c r="W27" s="3" t="s">
-        <v>31</v>
+        <v>275</v>
       </c>
       <c r="X27" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y27" s="1">
         <v>9930806009</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA27" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB27" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC27" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD27" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE27" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="28" spans="1:31" ht="22.2" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B28" s="3">
         <v>12371</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F28" s="3">
         <v>4</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L28" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="M28" s="19">
         <v>44968</v>
@@ -18442,13 +18436,13 @@
         <v>10</v>
       </c>
       <c r="R28" s="13" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="S28" s="19">
         <v>46032</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="U28" s="20">
         <v>7611</v>
@@ -18457,32 +18451,32 @@
         <v>30444</v>
       </c>
       <c r="W28" s="3" t="s">
-        <v>7</v>
+        <v>275</v>
       </c>
       <c r="X28" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Y28" s="1">
         <v>9930806009</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="AA28" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AB28" s="15" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve"> 400607</v>
       </c>
       <c r="AC28" s="15" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="AD28" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE28" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -18543,33 +18537,33 @@
   <sheetData>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C4" s="9">
         <v>10936</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E4" s="9">
         <v>1</v>
@@ -18577,7 +18571,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C5" s="9" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E5" s="9">
         <v>1</v>
@@ -18588,7 +18582,7 @@
         <v>13500</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E6" s="9">
         <v>2</v>
@@ -18596,7 +18590,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C7" s="9" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E7" s="9">
         <v>2</v>
@@ -18604,7 +18598,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B8" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E8" s="9">
         <v>3</v>
@@ -18612,7 +18606,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="E9" s="9">
         <v>3</v>
@@ -18620,16 +18614,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C10" s="9">
         <v>46611.6</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E10" s="9">
         <v>1</v>
@@ -18637,7 +18631,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C11" s="9" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E11" s="9">
         <v>1</v>
@@ -18645,7 +18639,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B12" s="9" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="E12" s="9">
         <v>1</v>
@@ -18653,13 +18647,13 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C13" s="9">
         <v>42174</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E13" s="9">
         <v>2</v>
@@ -18667,7 +18661,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C14" s="9" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E14" s="9">
         <v>2</v>
@@ -18675,7 +18669,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B15" s="9" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="E15" s="9">
         <v>2</v>
@@ -18683,7 +18677,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E16" s="9">
         <v>3</v>
@@ -18691,16 +18685,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C17" s="9">
         <v>23062</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E17" s="9">
         <v>2</v>
@@ -18708,7 +18702,7 @@
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C18" s="9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E18" s="9">
         <v>2</v>
@@ -18716,7 +18710,7 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B19" s="9" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E19" s="9">
         <v>2</v>
@@ -18724,7 +18718,7 @@
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E20" s="9">
         <v>2</v>
@@ -18732,16 +18726,16 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C21" s="9">
         <v>5347</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E21" s="9">
         <v>5</v>
@@ -18749,7 +18743,7 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C22" s="9" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E22" s="9">
         <v>5</v>
@@ -18757,7 +18751,7 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B23" s="9" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E23" s="9">
         <v>5</v>
@@ -18765,7 +18759,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E24" s="9">
         <v>5</v>
@@ -18773,16 +18767,16 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" s="9">
         <v>3050</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E25" s="9">
         <v>4</v>
@@ -18790,7 +18784,7 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C26" s="9" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="E26" s="9">
         <v>4</v>
@@ -18798,7 +18792,7 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B27" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E27" s="9">
         <v>4</v>
@@ -18806,7 +18800,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="E28" s="9">
         <v>4</v>
@@ -18814,16 +18808,16 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C29" s="9">
         <v>10311.291428571429</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E29" s="9">
         <v>2</v>
@@ -18831,7 +18825,7 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C30" s="9" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E30" s="9">
         <v>2</v>
@@ -18839,7 +18833,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B31" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E31" s="9">
         <v>2</v>
@@ -18847,7 +18841,7 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="E32" s="9">
         <v>2</v>
@@ -18855,16 +18849,16 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="9" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C33" s="9">
         <v>15697.731428571427</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E33" s="9">
         <v>2</v>
@@ -18872,7 +18866,7 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C34" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E34" s="9">
         <v>2</v>
@@ -18880,7 +18874,7 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B35" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E35" s="9">
         <v>2</v>
@@ -18888,7 +18882,7 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E36" s="9">
         <v>2</v>
@@ -18896,16 +18890,16 @@
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C37" s="9">
         <v>7611</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E37" s="9">
         <v>1</v>
@@ -18913,7 +18907,7 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C38" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E38" s="9">
         <v>1</v>
@@ -18921,7 +18915,7 @@
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B39" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E39" s="9">
         <v>1</v>
@@ -18929,7 +18923,7 @@
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="9" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="E40" s="9">
         <v>1</v>
@@ -18937,16 +18931,16 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="9" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C41" s="9">
         <v>52100</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E41" s="9">
         <v>1</v>
@@ -18954,7 +18948,7 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C42" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E42" s="9">
         <v>1</v>
@@ -18962,7 +18956,7 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B43" s="9" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E43" s="9">
         <v>1</v>
@@ -18970,13 +18964,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B44" s="9" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C44" s="9">
         <v>52100</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E44" s="9">
         <v>1</v>
@@ -18984,7 +18978,7 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C45" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E45" s="9">
         <v>1</v>
@@ -18992,7 +18986,7 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B46" s="9" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="E46" s="9">
         <v>1</v>
@@ -19000,13 +18994,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B47" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C47" s="9">
         <v>40800</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E47" s="9">
         <v>1</v>
@@ -19014,7 +19008,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C48" s="9" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="E48" s="9">
         <v>1</v>
@@ -19022,7 +19016,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B49" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E49" s="9">
         <v>1</v>
@@ -19030,7 +19024,7 @@
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="E50" s="9">
         <v>3</v>
@@ -19038,16 +19032,16 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="9" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C51" s="9">
         <v>52100</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E51" s="9">
         <v>1</v>
@@ -19055,7 +19049,7 @@
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C52" s="9" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="E52" s="9">
         <v>1</v>
@@ -19063,7 +19057,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B53" s="9" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="E53" s="9">
         <v>1</v>
@@ -19071,7 +19065,7 @@
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="E54" s="9">
         <v>1</v>
@@ -19079,16 +19073,16 @@
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="9" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" s="9">
         <v>6530</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E55" s="9">
         <v>1</v>
@@ -19096,7 +19090,7 @@
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C56" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E56" s="9">
         <v>1</v>
@@ -19104,7 +19098,7 @@
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B57" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E57" s="9">
         <v>1</v>
@@ -19112,7 +19106,7 @@
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E58" s="9">
         <v>1</v>
@@ -19120,16 +19114,16 @@
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="9" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C59" s="9">
         <v>53908</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E59" s="9">
         <v>1</v>
@@ -19137,7 +19131,7 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C60" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E60" s="9">
         <v>1</v>
@@ -19145,7 +19139,7 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B61" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E61" s="9">
         <v>1</v>
@@ -19153,7 +19147,7 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E62" s="9">
         <v>1</v>
@@ -19161,16 +19155,16 @@
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C63" s="9">
         <v>8931</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E63" s="9">
         <v>8</v>
@@ -19178,7 +19172,7 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C64" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E64" s="9">
         <v>8</v>
@@ -19186,7 +19180,7 @@
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B65" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E65" s="9">
         <v>8</v>
@@ -19194,7 +19188,7 @@
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E66" s="9">
         <v>8</v>
@@ -19202,16 +19196,16 @@
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="9" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C67" s="9">
         <v>3600</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E67" s="9">
         <v>5</v>
@@ -19219,7 +19213,7 @@
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C68" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E68" s="9">
         <v>5</v>
@@ -19227,7 +19221,7 @@
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B69" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E69" s="9">
         <v>5</v>
@@ -19235,7 +19229,7 @@
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="9" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E70" s="9">
         <v>5</v>
@@ -19243,16 +19237,16 @@
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="B71" s="9" t="s">
         <v>124</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="C71" s="9">
         <v>135535.88888888888</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E71" s="9">
         <v>2</v>
@@ -19260,7 +19254,7 @@
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C72" s="9" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="E72" s="9">
         <v>2</v>
@@ -19268,7 +19262,7 @@
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B73" s="9" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E73" s="9">
         <v>2</v>
@@ -19276,7 +19270,7 @@
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E74" s="9">
         <v>2</v>
@@ -19284,16 +19278,16 @@
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C75" s="9">
         <v>425465</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E75" s="9">
         <v>1</v>
@@ -19301,7 +19295,7 @@
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C76" s="9" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E76" s="9">
         <v>1</v>
@@ -19312,7 +19306,7 @@
         <v>650472</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E77" s="9">
         <v>1</v>
@@ -19320,7 +19314,7 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C78" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E78" s="9">
         <v>1</v>
@@ -19328,7 +19322,7 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B79" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E79" s="9">
         <v>2</v>
@@ -19336,7 +19330,7 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="9" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E80" s="9">
         <v>2</v>
@@ -19344,16 +19338,16 @@
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="9" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C81" s="9">
         <v>44925.227272727272</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E81" s="9">
         <v>22</v>
@@ -19361,7 +19355,7 @@
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C82" s="9" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="E82" s="9">
         <v>22</v>
@@ -19369,7 +19363,7 @@
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B83" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E83" s="9">
         <v>22</v>
@@ -19377,7 +19371,7 @@
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E84" s="9">
         <v>22</v>
@@ -19385,16 +19379,16 @@
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="9" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C85" s="9">
         <v>15697.731428571427</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E85" s="9">
         <v>1</v>
@@ -19402,7 +19396,7 @@
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C86" s="9" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="E86" s="9">
         <v>1</v>
@@ -19410,7 +19404,7 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B87" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E87" s="9">
         <v>1</v>
@@ -19418,7 +19412,7 @@
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E88" s="9">
         <v>1</v>
@@ -19426,16 +19420,16 @@
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C89" s="9">
         <v>50000</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E89" s="9">
         <v>1</v>
@@ -19443,7 +19437,7 @@
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C90" s="9" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="E90" s="9">
         <v>1</v>
@@ -19451,7 +19445,7 @@
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B91" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E91" s="9">
         <v>1</v>
@@ -19459,7 +19453,7 @@
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="9" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="E92" s="9">
         <v>1</v>
@@ -19467,16 +19461,16 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C93" s="9">
         <v>9617</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E93" s="9">
         <v>1</v>
@@ -19484,7 +19478,7 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C94" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="E94" s="9">
         <v>1</v>
@@ -19492,7 +19486,7 @@
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B95" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E95" s="9">
         <v>1</v>
@@ -19500,7 +19494,7 @@
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="9" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="E96" s="9">
         <v>1</v>
@@ -19508,16 +19502,16 @@
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C97" s="9">
         <v>7611</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E97" s="9">
         <v>1</v>
@@ -19525,7 +19519,7 @@
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C98" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E98" s="9">
         <v>1</v>
@@ -19536,7 +19530,7 @@
         <v>8201</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E99" s="9">
         <v>6</v>
@@ -19544,7 +19538,7 @@
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C100" s="9" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E100" s="9">
         <v>6</v>
@@ -19552,7 +19546,7 @@
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B101" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E101" s="9">
         <v>7</v>
@@ -19560,7 +19554,7 @@
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="9" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E102" s="9">
         <v>7</v>
@@ -19568,16 +19562,16 @@
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C103" s="9">
         <v>1400</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E103" s="9">
         <v>1</v>
@@ -19585,7 +19579,7 @@
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C104" s="9" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E104" s="9">
         <v>1</v>
@@ -19593,7 +19587,7 @@
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B105" s="9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E105" s="9">
         <v>1</v>
@@ -19601,7 +19595,7 @@
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="E106" s="9">
         <v>1</v>
@@ -19609,16 +19603,16 @@
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B107" s="9" t="s">
         <v>26</v>
-      </c>
-      <c r="B107" s="9" t="s">
-        <v>27</v>
       </c>
       <c r="C107" s="9">
         <v>9950</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E107" s="9">
         <v>1</v>
@@ -19626,7 +19620,7 @@
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C108" s="9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="E108" s="9">
         <v>1</v>
@@ -19637,7 +19631,7 @@
         <v>13516</v>
       </c>
       <c r="D109" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E109" s="9">
         <v>2</v>
@@ -19645,7 +19639,7 @@
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C110" s="9" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E110" s="9">
         <v>2</v>
@@ -19653,7 +19647,7 @@
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B111" s="9" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="E111" s="9">
         <v>3</v>
@@ -19661,7 +19655,7 @@
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="E112" s="9">
         <v>3</v>
@@ -19669,16 +19663,16 @@
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C113" s="9">
         <v>55440</v>
       </c>
       <c r="D113" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E113" s="9">
         <v>1</v>
@@ -19686,7 +19680,7 @@
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C114" s="9" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="E114" s="9">
         <v>1</v>
@@ -19694,7 +19688,7 @@
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B115" s="9" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="E115" s="9">
         <v>1</v>
@@ -19702,7 +19696,7 @@
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="9" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="E116" s="9">
         <v>1</v>
@@ -19710,16 +19704,16 @@
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C117" s="9">
         <v>2821.375</v>
       </c>
       <c r="D117" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E117" s="9">
         <v>1</v>
@@ -19727,7 +19721,7 @@
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C118" s="9" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E118" s="9">
         <v>1</v>
@@ -19735,7 +19729,7 @@
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B119" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E119" s="9">
         <v>1</v>
@@ -19743,7 +19737,7 @@
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="E120" s="9">
         <v>1</v>
@@ -19751,16 +19745,16 @@
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C121" s="9">
         <v>6500</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E121" s="9">
         <v>2</v>
@@ -19768,7 +19762,7 @@
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C122" s="9" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="E122" s="9">
         <v>2</v>
@@ -19776,7 +19770,7 @@
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B123" s="9" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="E123" s="9">
         <v>2</v>
@@ -19784,7 +19778,7 @@
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" s="9" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E124" s="9">
         <v>2</v>
@@ -19792,16 +19786,16 @@
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C125" s="9">
         <v>24319.771428571428</v>
       </c>
       <c r="D125" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E125" s="9">
         <v>2</v>
@@ -19809,7 +19803,7 @@
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C126" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="E126" s="9">
         <v>2</v>
@@ -19820,7 +19814,7 @@
         <v>31426</v>
       </c>
       <c r="D127" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E127" s="9">
         <v>6</v>
@@ -19828,7 +19822,7 @@
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C128" s="9" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="E128" s="9">
         <v>6</v>
@@ -19836,7 +19830,7 @@
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B129" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E129" s="9">
         <v>8</v>
@@ -19844,7 +19838,7 @@
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" s="9" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="E130" s="9">
         <v>8</v>
@@ -19852,16 +19846,16 @@
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C131" s="9">
         <v>19305</v>
       </c>
       <c r="D131" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E131" s="9">
         <v>1</v>
@@ -19869,7 +19863,7 @@
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C132" s="9" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="E132" s="9">
         <v>1</v>
@@ -19877,7 +19871,7 @@
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B133" s="9" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="E133" s="9">
         <v>1</v>
@@ -19885,7 +19879,7 @@
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" s="9" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E134" s="9">
         <v>1</v>
@@ -19893,16 +19887,16 @@
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B135" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C135" s="9">
         <v>5900</v>
       </c>
       <c r="D135" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E135" s="9">
         <v>1</v>
@@ -19910,7 +19904,7 @@
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C136" s="9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="E136" s="9">
         <v>1</v>
@@ -19921,7 +19915,7 @@
         <v>20022</v>
       </c>
       <c r="D137" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E137" s="9">
         <v>3</v>
@@ -19929,7 +19923,7 @@
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C138" s="9" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="E138" s="9">
         <v>3</v>
@@ -19937,7 +19931,7 @@
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B139" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E139" s="9">
         <v>4</v>
@@ -19945,13 +19939,13 @@
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B140" s="9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C140" s="9">
         <v>34567.231428571431</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E140" s="9">
         <v>1</v>
@@ -19959,7 +19953,7 @@
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C141" s="9" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="E141" s="9">
         <v>1</v>
@@ -19970,7 +19964,7 @@
         <v>34568.231428571402</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E142" s="9">
         <v>2</v>
@@ -19978,7 +19972,7 @@
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C143" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E143" s="9">
         <v>2</v>
@@ -19986,7 +19980,7 @@
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B144" s="9" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E144" s="9">
         <v>3</v>
@@ -19994,7 +19988,7 @@
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="9" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="E145" s="9">
         <v>7</v>
@@ -20002,16 +19996,16 @@
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="9" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B146" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C146" s="9">
         <v>27441</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E146" s="9">
         <v>83</v>
@@ -20019,7 +20013,7 @@
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C147" s="9" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="E147" s="9">
         <v>83</v>
@@ -20027,7 +20021,7 @@
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B148" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E148" s="9">
         <v>83</v>
@@ -20035,7 +20029,7 @@
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" s="9" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E149" s="9">
         <v>83</v>
@@ -20043,16 +20037,16 @@
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="B150" s="9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C150" s="9">
         <v>13150</v>
       </c>
       <c r="D150" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E150" s="9">
         <v>1</v>
@@ -20060,7 +20054,7 @@
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C151" s="9" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="E151" s="9">
         <v>1</v>
@@ -20068,7 +20062,7 @@
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B152" s="9" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E152" s="9">
         <v>1</v>
@@ -20076,7 +20070,7 @@
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="9" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E153" s="9">
         <v>1</v>
@@ -20084,16 +20078,16 @@
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" s="9" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B154" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C154" s="9">
         <v>6530</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E154" s="9">
         <v>1</v>
@@ -20101,7 +20095,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C155" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E155" s="9">
         <v>1</v>
@@ -20109,7 +20103,7 @@
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B156" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E156" s="9">
         <v>1</v>
@@ -20117,7 +20111,7 @@
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" s="9" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E157" s="9">
         <v>1</v>
@@ -20125,16 +20119,16 @@
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" s="9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B158" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C158" s="9">
         <v>5000</v>
       </c>
       <c r="D158" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E158" s="9">
         <v>3</v>
@@ -20142,7 +20136,7 @@
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C159" s="9" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="E159" s="9">
         <v>3</v>
@@ -20150,7 +20144,7 @@
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B160" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E160" s="9">
         <v>3</v>
@@ -20158,7 +20152,7 @@
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E161" s="9">
         <v>3</v>
@@ -20166,16 +20160,16 @@
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" s="9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B162" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C162" s="9">
         <v>7611</v>
       </c>
       <c r="D162" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E162" s="9">
         <v>13</v>
@@ -20183,7 +20177,7 @@
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C163" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E163" s="9">
         <v>13</v>
@@ -20191,7 +20185,7 @@
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B164" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E164" s="9">
         <v>13</v>
@@ -20199,13 +20193,13 @@
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B165" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C165" s="9">
         <v>7611</v>
       </c>
       <c r="D165" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E165" s="9">
         <v>4</v>
@@ -20213,7 +20207,7 @@
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C166" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E166" s="9">
         <v>4</v>
@@ -20221,7 +20215,7 @@
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B167" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E167" s="9">
         <v>4</v>
@@ -20229,7 +20223,7 @@
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" s="9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E168" s="9">
         <v>17</v>
@@ -20237,16 +20231,16 @@
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C169" s="9">
         <v>62722</v>
       </c>
       <c r="D169" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E169" s="9">
         <v>1</v>
@@ -20254,7 +20248,7 @@
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C170" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E170" s="9">
         <v>1</v>
@@ -20262,7 +20256,7 @@
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B171" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E171" s="9">
         <v>1</v>
@@ -20270,7 +20264,7 @@
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" s="9" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E172" s="9">
         <v>1</v>
@@ -20278,16 +20272,16 @@
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C173" s="9">
         <v>57454.75</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E173" s="9">
         <v>1</v>
@@ -20295,7 +20289,7 @@
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C174" s="9" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E174" s="9">
         <v>1</v>
@@ -20306,7 +20300,7 @@
         <v>62722</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E175" s="9">
         <v>2</v>
@@ -20314,7 +20308,7 @@
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C176" s="9" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E176" s="9">
         <v>2</v>
@@ -20322,7 +20316,7 @@
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B177" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E177" s="9">
         <v>3</v>
@@ -20330,7 +20324,7 @@
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" s="9" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="E178" s="9">
         <v>3</v>
@@ -20338,16 +20332,16 @@
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C179" s="9">
         <v>34567</v>
       </c>
       <c r="D179" s="9" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E179" s="9">
         <v>1</v>
@@ -20355,7 +20349,7 @@
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C180" s="9" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="E180" s="9">
         <v>1</v>
@@ -20366,7 +20360,7 @@
         <v>34568.231428571402</v>
       </c>
       <c r="D181" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E181" s="9">
         <v>3</v>
@@ -20374,7 +20368,7 @@
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C182" s="9" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="E182" s="9">
         <v>3</v>
@@ -20382,7 +20376,7 @@
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B183" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E183" s="9">
         <v>4</v>
@@ -20390,7 +20384,7 @@
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" s="9" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E184" s="9">
         <v>4</v>
@@ -20398,16 +20392,16 @@
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" s="9" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C185" s="9">
         <v>9405</v>
       </c>
       <c r="D185" s="9" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E185" s="9">
         <v>4</v>
@@ -20415,7 +20409,7 @@
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C186" s="9" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="E186" s="9">
         <v>4</v>
@@ -20423,7 +20417,7 @@
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B187" s="9" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E187" s="9">
         <v>4</v>
@@ -20431,7 +20425,7 @@
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" s="9" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E188" s="9">
         <v>4</v>
@@ -20439,7 +20433,7 @@
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" s="9" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E189" s="9">
         <v>218</v>
